--- a/outputs_xlsx_solution/test_new2.4-wide-NF-1.xlsx
+++ b/outputs_xlsx_solution/test_new2.4-wide-NF-1.xlsx
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -984,10 +990,26 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
